--- a/results/03-2026/beta/inputs-03-2026.xlsx
+++ b/results/03-2026/beta/inputs-03-2026.xlsx
@@ -3695,7 +3695,7 @@
         <v>4.222</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.80364</v>
+        <v>2.8036115</v>
       </c>
       <c r="AG20" t="n">
         <v>0.7</v>
@@ -3746,7 +3746,7 @@
         <v>6.35096</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.21888887</v>
+        <v>8.21888317</v>
       </c>
       <c r="AX20" t="n">
         <v>0.4014</v>
@@ -3853,7 +3853,7 @@
         <v>2.372</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.833375</v>
+        <v>2.833394</v>
       </c>
       <c r="AG21" t="n">
         <v>0.7</v>
@@ -3904,7 +3904,7 @@
         <v>4.56094</v>
       </c>
       <c r="AW21" t="n">
-        <v>6.19030152</v>
+        <v>6.190300475</v>
       </c>
       <c r="AX21" t="n">
         <v>0.4023</v>
@@ -4011,7 +4011,7 @@
         <v>2.372</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.823948</v>
+        <v>2.8239574</v>
       </c>
       <c r="AG22" t="n">
         <v>0.7</v>
@@ -4062,7 +4062,7 @@
         <v>3.85754</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.1270965</v>
+        <v>4.12709705</v>
       </c>
       <c r="AX22" t="n">
         <v>0.3861</v>
@@ -4169,7 +4169,7 @@
         <v>2.372</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.865684</v>
+        <v>2.8656558</v>
       </c>
       <c r="AG23" t="n">
         <v>0.7</v>
@@ -4220,7 +4220,7 @@
         <v>3.17264</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.47882573</v>
+        <v>2.478820453</v>
       </c>
       <c r="AX23" t="n">
         <v>0.315</v>
@@ -4327,7 +4327,7 @@
         <v>2.372</v>
       </c>
       <c r="AF24" t="n">
-        <v>-8.089008</v>
+        <v>-8.076788</v>
       </c>
       <c r="AG24" t="n">
         <v>0.7</v>
@@ -4378,7 +4378,7 @@
         <v>2.58402</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.34183368</v>
+        <v>0.344274675</v>
       </c>
       <c r="AX24" t="n">
         <v>0.315</v>
@@ -4536,7 +4536,7 @@
         <v>2.04112</v>
       </c>
       <c r="AW25" t="n">
-        <v>-1.47547052</v>
+        <v>-1.473395937</v>
       </c>
       <c r="AX25" t="n">
         <v>0.315</v>
@@ -4595,7 +4595,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P26" t="n">
-        <v>3401.30978935855</v>
+        <v>0.5</v>
       </c>
       <c r="Q26" t="n">
         <v>5098.38692298557</v>
@@ -4694,7 +4694,7 @@
         <v>1.53068</v>
       </c>
       <c r="AW26" t="n">
-        <v>-3.19731131</v>
+        <v>-3.195359969</v>
       </c>
       <c r="AX26" t="n">
         <v>0.28035</v>
@@ -4753,7 +4753,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P27" t="n">
-        <v>3433.77518475659</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
         <v>5136.57982245723</v>
@@ -4852,7 +4852,7 @@
         <v>1.05376</v>
       </c>
       <c r="AW27" t="n">
-        <v>-4.80902829</v>
+        <v>-4.807197548</v>
       </c>
       <c r="AX27" t="n">
         <v>0.250425</v>
@@ -4911,7 +4911,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P28" t="n">
-        <v>3466.99256859914</v>
+        <v>0.5</v>
       </c>
       <c r="Q28" t="n">
         <v>5175.12973428041</v>
@@ -5010,7 +5010,7 @@
         <v>0.61906</v>
       </c>
       <c r="AW28" t="n">
-        <v>-6.37856472</v>
+        <v>-6.3774651</v>
       </c>
       <c r="AX28" t="n">
         <v>0.222075</v>
@@ -5069,7 +5069,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P29" t="n">
-        <v>3497.5971870629</v>
+        <v>0.3</v>
       </c>
       <c r="Q29" t="n">
         <v>5209.63879652421</v>
@@ -5168,7 +5168,7 @@
         <v>0.37618</v>
       </c>
       <c r="AW29" t="n">
-        <v>-7.42323798</v>
+        <v>-7.422628014</v>
       </c>
       <c r="AX29" t="n">
         <v>0.1953</v>
@@ -5227,7 +5227,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P30" t="n">
-        <v>3529.55305909616</v>
+        <v>0.4</v>
       </c>
       <c r="Q30" t="n">
         <v>5456.24117371526</v>
@@ -5326,7 +5326,7 @@
         <v>0.23798</v>
       </c>
       <c r="AW30" t="n">
-        <v>-8.44170484</v>
+        <v>-8.441094968</v>
       </c>
       <c r="AX30" t="n">
         <v>0.171675</v>
@@ -5385,7 +5385,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P31" t="n">
-        <v>3561.43162500994</v>
+        <v>0.5</v>
       </c>
       <c r="Q31" t="n">
         <v>5492.13433341532</v>
@@ -5484,7 +5484,7 @@
         <v>0.11938</v>
       </c>
       <c r="AW31" t="n">
-        <v>-9.32572512</v>
+        <v>-9.32523632</v>
       </c>
       <c r="AX31" t="n">
         <v>0.14805</v>
@@ -5543,7 +5543,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P32" t="n">
-        <v>3592.17594462895</v>
+        <v>0.4</v>
       </c>
       <c r="Q32" t="n">
         <v>5528.30528728337</v>
@@ -5701,7 +5701,7 @@
         <v>75.1961428571429</v>
       </c>
       <c r="P33" t="n">
-        <v>3622.79177047259</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" t="n">
         <v>5563.98496925483</v>
